--- a/Config/GameConfig/Datas/farmland/seed.xlsx
+++ b/Config/GameConfig/Datas/farmland/seed.xlsx
@@ -8,24 +8,35 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UnityProject\Framework\Framework\Config\GameConfig\Datas\farmland\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECBE9739-F2E5-4AF1-8B39-E823D3CC5654}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E6B0DDD-DE07-4AB2-A3FE-F200C783116C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="62">
   <si>
     <t>##var</t>
   </si>
@@ -149,10 +160,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>最低产量(被偷后)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>最多浇水次数</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -221,10 +228,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>item.ItemExchange</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>##var</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -233,11 +236,99 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Count</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>list,int</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>needWaterTime</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>min</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>max</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>item.ItemExchangeRange</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MinCount</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxCount</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>PestRate</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>虫害出现概率,100代表100%</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>seedType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>farm.ESeedType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>作物类型</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Paddy</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dry</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>##</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>最低产量比例(被偷后)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>50代表50%，表示至少剩下原产量的50%</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mutiHarvestYieldCountChangeRate</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>多季收获产量变化率,可以负数，0表示与第一次收获产量一致</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>rareRate</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>稀有收获概率</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1 = 1%</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>rareYieldCount</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>触发稀有收获的额外产量</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -303,7 +394,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -327,14 +418,16 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
+      <left/>
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top/>
-      <bottom/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -347,12 +440,27 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
-      <right style="thin">
+      <right/>
+      <top style="thin">
         <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -365,31 +473,51 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -674,250 +802,419 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:AK9"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="19.875" customWidth="1"/>
     <col min="5" max="6" width="13.625" customWidth="1"/>
-    <col min="7" max="7" width="23.25" customWidth="1"/>
-    <col min="8" max="8" width="16.25" customWidth="1"/>
-    <col min="9" max="9" width="14.875" customWidth="1"/>
-    <col min="10" max="10" width="22.75" customWidth="1"/>
-    <col min="11" max="11" width="17.75" customWidth="1"/>
-    <col min="12" max="12" width="21" customWidth="1"/>
-    <col min="13" max="13" width="18.375" customWidth="1"/>
-    <col min="14" max="14" width="19.25" customWidth="1"/>
-    <col min="15" max="17" width="15.625" customWidth="1"/>
+    <col min="7" max="7" width="21.375" customWidth="1"/>
+    <col min="8" max="8" width="23.25" customWidth="1"/>
+    <col min="9" max="9" width="16.25" customWidth="1"/>
+    <col min="10" max="11" width="14.875" customWidth="1"/>
+    <col min="12" max="12" width="39.125" customWidth="1"/>
+    <col min="13" max="15" width="18" customWidth="1"/>
+    <col min="16" max="16" width="19.625" customWidth="1"/>
+    <col min="17" max="18" width="22.75" customWidth="1"/>
+    <col min="19" max="19" width="17.75" customWidth="1"/>
+    <col min="20" max="20" width="21" customWidth="1"/>
+    <col min="21" max="21" width="23.25" customWidth="1"/>
+    <col min="22" max="22" width="18.375" customWidth="1"/>
+    <col min="23" max="23" width="19.25" customWidth="1"/>
+    <col min="24" max="24" width="10.75" customWidth="1"/>
+    <col min="25" max="25" width="10.125" customWidth="1"/>
+    <col min="26" max="26" width="9.375" customWidth="1"/>
+    <col min="29" max="29" width="11.25" customWidth="1"/>
+    <col min="30" max="30" width="11.125" customWidth="1"/>
+    <col min="31" max="31" width="11.875" customWidth="1"/>
+    <col min="32" max="32" width="12.5" customWidth="1"/>
+    <col min="33" max="33" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>16</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I1" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="I1" s="6"/>
-      <c r="J1" s="1" t="s">
+      <c r="M1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="N1" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="O1" s="14"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="R1" s="7"/>
+      <c r="S1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="U1" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="V1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="X1" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="Y1" s="7"/>
+      <c r="Z1" s="7"/>
+      <c r="AA1" s="7"/>
+      <c r="AB1" s="7"/>
+      <c r="AC1" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD1" s="7"/>
+      <c r="AE1" s="7"/>
+      <c r="AF1" s="7"/>
+      <c r="AG1" s="7"/>
+    </row>
+    <row r="2" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="P1" s="10"/>
-      <c r="Q1" s="10"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="4"/>
+      <c r="T2" s="4"/>
+      <c r="U2" s="4"/>
+      <c r="V2" s="4"/>
+      <c r="W2" s="4"/>
+      <c r="X2" s="9"/>
+      <c r="Y2" s="9"/>
+      <c r="Z2" s="9"/>
+      <c r="AA2" s="9"/>
+      <c r="AB2" s="9"/>
+      <c r="AC2" s="10"/>
+      <c r="AD2" s="12"/>
+      <c r="AE2" s="12"/>
+      <c r="AF2" s="12"/>
+      <c r="AG2" s="12"/>
+      <c r="AI2" s="6"/>
+      <c r="AJ2" s="6"/>
+      <c r="AK2" s="6"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="H2" t="s">
-        <v>39</v>
-      </c>
-      <c r="I2" t="s">
-        <v>40</v>
-      </c>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="2" t="s">
         <v>5</v>
       </c>
       <c r="G3" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="I3" s="9"/>
-      <c r="J3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="I3" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
       <c r="L3" s="2" t="s">
         <v>17</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="N3" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="O3" s="8"/>
+      <c r="P3" s="8"/>
+      <c r="Q3" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="R3" s="8"/>
+      <c r="S3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="O3" s="8" t="s">
+      <c r="T3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="U3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="X3" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y3" s="8"/>
+      <c r="Z3" s="8"/>
+      <c r="AA3" s="8"/>
+      <c r="AB3" s="8"/>
+      <c r="AC3" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD3" s="8"/>
+      <c r="AE3" s="8"/>
+      <c r="AF3" s="8"/>
+      <c r="AG3" s="8"/>
+    </row>
+    <row r="4" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="2"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="16"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="11"/>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="4"/>
+      <c r="S4" s="4"/>
+      <c r="T4" s="4"/>
+      <c r="U4" s="4"/>
+      <c r="V4" s="4"/>
+      <c r="W4" s="4"/>
+      <c r="X4" s="9"/>
+      <c r="Y4" s="9"/>
+      <c r="Z4" s="9"/>
+      <c r="AA4" s="9"/>
+      <c r="AB4" s="9"/>
+      <c r="AC4" s="10"/>
+      <c r="AD4" s="6"/>
+      <c r="AE4" s="6"/>
+      <c r="AF4" s="6"/>
+      <c r="AG4" s="6"/>
+    </row>
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="N5" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="O5" s="14"/>
+      <c r="P5" s="15"/>
+      <c r="Q5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="R5" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="P3" s="11"/>
-      <c r="Q3" s="11"/>
+      <c r="S5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="V5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X5" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y5" s="7"/>
+      <c r="Z5" s="7"/>
+      <c r="AA5" s="7"/>
+      <c r="AB5" s="7"/>
+      <c r="AC5" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="AD5" s="7"/>
+      <c r="AE5" s="7"/>
+      <c r="AF5" s="7"/>
+      <c r="AG5" s="7"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="s">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+      <c r="T6" s="1"/>
+      <c r="U6" s="1"/>
+      <c r="V6" s="1"/>
+      <c r="W6" s="1"/>
+      <c r="X6" s="3">
+        <v>2</v>
+      </c>
+      <c r="Y6" s="3">
+        <v>3</v>
+      </c>
+      <c r="Z6" s="3">
+        <v>4</v>
+      </c>
+      <c r="AA6" s="3">
+        <v>5</v>
+      </c>
+      <c r="AB6" s="3">
         <v>6</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="O4" s="7"/>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="7"/>
+      <c r="AC6" s="3">
+        <v>2</v>
+      </c>
+      <c r="AD6" s="3">
+        <v>3</v>
+      </c>
+      <c r="AE6" s="3">
+        <v>4</v>
+      </c>
+      <c r="AF6" s="3">
+        <v>5</v>
+      </c>
+      <c r="AG6" s="3">
+        <v>6</v>
+      </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I5" s="6"/>
-      <c r="J5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O5" s="5" t="s">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="B7">
+        <v>1100001</v>
+      </c>
+      <c r="C7" t="s">
         <v>24</v>
-      </c>
-      <c r="P5" s="10"/>
-      <c r="Q5" s="10"/>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B6">
-        <v>1100001</v>
-      </c>
-      <c r="C6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-      <c r="H6">
-        <v>1110001</v>
-      </c>
-      <c r="I6">
-        <v>5</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="K6">
-        <v>3</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B7">
-        <v>1100002</v>
-      </c>
-      <c r="C7" t="s">
-        <v>26</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -926,93 +1223,232 @@
         <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7">
+        <v>24</v>
+      </c>
+      <c r="G7" t="s">
+        <v>50</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7">
+        <v>1110001</v>
+      </c>
+      <c r="J7">
+        <v>5</v>
+      </c>
+      <c r="K7">
         <v>10</v>
       </c>
-      <c r="H7">
-        <v>1110002</v>
-      </c>
-      <c r="I7">
-        <v>4</v>
-      </c>
-      <c r="J7">
+      <c r="L7">
+        <v>50</v>
+      </c>
+      <c r="M7">
         <v>1</v>
       </c>
-      <c r="K7">
+      <c r="N7">
+        <v>1110001</v>
+      </c>
+      <c r="O7">
+        <v>20</v>
+      </c>
+      <c r="P7">
+        <v>30</v>
+      </c>
+      <c r="Q7">
         <v>2</v>
       </c>
-      <c r="L7">
+      <c r="R7">
+        <v>3</v>
+      </c>
+      <c r="S7">
         <v>2</v>
       </c>
-      <c r="M7">
-        <v>2</v>
-      </c>
-      <c r="N7">
+      <c r="T7">
         <v>1</v>
       </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>1</v>
+      </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B8">
-        <v>1100003</v>
+        <v>1100002</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" t="s">
+        <v>51</v>
+      </c>
+      <c r="H8">
+        <v>10</v>
+      </c>
+      <c r="I8">
+        <v>1110002</v>
+      </c>
+      <c r="J8">
+        <v>6</v>
+      </c>
+      <c r="K8">
+        <v>12</v>
+      </c>
+      <c r="L8">
+        <v>50</v>
+      </c>
+      <c r="M8">
+        <v>3</v>
+      </c>
+      <c r="N8">
+        <v>1110002</v>
+      </c>
+      <c r="O8">
+        <v>25</v>
+      </c>
+      <c r="P8">
+        <v>40</v>
+      </c>
+      <c r="Q8">
         <v>2</v>
       </c>
-      <c r="F8" t="s">
-        <v>27</v>
-      </c>
-      <c r="G8">
+      <c r="R8">
+        <v>4</v>
+      </c>
+      <c r="S8">
+        <v>2</v>
+      </c>
+      <c r="T8">
+        <v>2</v>
+      </c>
+      <c r="U8">
+        <v>15</v>
+      </c>
+      <c r="V8">
+        <v>2</v>
+      </c>
+      <c r="W8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="B9">
+        <v>1100003</v>
+      </c>
+      <c r="C9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>2</v>
+      </c>
+      <c r="F9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H9">
         <v>20</v>
       </c>
-      <c r="H8">
+      <c r="I9">
         <v>1110003</v>
       </c>
-      <c r="I8">
+      <c r="J9">
+        <v>7</v>
+      </c>
+      <c r="K9">
+        <v>15</v>
+      </c>
+      <c r="L9">
+        <v>50</v>
+      </c>
+      <c r="M9">
+        <v>5</v>
+      </c>
+      <c r="N9">
+        <v>1110003</v>
+      </c>
+      <c r="O9">
+        <v>30</v>
+      </c>
+      <c r="P9">
+        <v>50</v>
+      </c>
+      <c r="Q9">
         <v>3</v>
       </c>
-      <c r="J8">
+      <c r="R9">
+        <v>5</v>
+      </c>
+      <c r="S9">
+        <v>3</v>
+      </c>
+      <c r="T9">
+        <v>2</v>
+      </c>
+      <c r="U9">
+        <v>25</v>
+      </c>
+      <c r="V9">
         <v>1</v>
       </c>
-      <c r="K8">
-        <v>1</v>
-      </c>
-      <c r="L8">
-        <v>2</v>
-      </c>
-      <c r="M8">
-        <v>1</v>
-      </c>
-      <c r="N8">
+      <c r="W9">
         <v>3</v>
       </c>
-      <c r="O8">
+      <c r="X9">
         <v>10</v>
       </c>
-      <c r="P8">
+      <c r="Y9">
         <v>5</v>
+      </c>
+      <c r="AC9">
+        <v>-30</v>
+      </c>
+      <c r="AD9">
+        <v>-50</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="O1:Q1"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="O3:Q3"/>
-    <mergeCell ref="O4:Q4"/>
-    <mergeCell ref="O5:Q5"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="J2:K2"/>
+  <mergeCells count="22">
+    <mergeCell ref="N1:P1"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="AI2:AK2"/>
+    <mergeCell ref="AC1:AG1"/>
+    <mergeCell ref="AC2:AG2"/>
+    <mergeCell ref="AC3:AG3"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="Q3:R3"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="X1:AB1"/>
+    <mergeCell ref="X2:AB2"/>
+    <mergeCell ref="X3:AB3"/>
+    <mergeCell ref="X4:AB4"/>
+    <mergeCell ref="X5:AB5"/>
+    <mergeCell ref="AC4:AG4"/>
+    <mergeCell ref="AC5:AG5"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/GameConfig/Datas/farmland/seed.xlsx
+++ b/Config/GameConfig/Datas/farmland/seed.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UnityProject\Framework\Framework\Config\GameConfig\Datas\farmland\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E6B0DDD-DE07-4AB2-A3FE-F200C783116C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5E9D45B-CB9C-4C03-A134-E757983FD961}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -484,27 +484,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -514,12 +493,31 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="差" xfId="2" builtinId="27"/>
@@ -827,7 +825,9 @@
     <col min="30" max="30" width="11.125" customWidth="1"/>
     <col min="31" max="31" width="11.875" customWidth="1"/>
     <col min="32" max="32" width="12.5" customWidth="1"/>
-    <col min="33" max="33" width="13" customWidth="1"/>
+    <col min="33" max="33" width="13.75" customWidth="1"/>
+    <col min="34" max="34" width="32" customWidth="1"/>
+    <col min="35" max="35" width="22.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37" x14ac:dyDescent="0.2">
@@ -855,26 +855,26 @@
       <c r="H1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
       <c r="L1" s="1" t="s">
         <v>30</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="N1" s="13" t="s">
+      <c r="N1" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="O1" s="14"/>
-      <c r="P1" s="15"/>
-      <c r="Q1" s="7" t="s">
+      <c r="O1" s="7"/>
+      <c r="P1" s="8"/>
+      <c r="Q1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="R1" s="7"/>
+      <c r="R1" s="14"/>
       <c r="S1" s="1" t="s">
         <v>31</v>
       </c>
@@ -890,20 +890,20 @@
       <c r="W1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="X1" s="7" t="s">
+      <c r="X1" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="Y1" s="7"/>
-      <c r="Z1" s="7"/>
-      <c r="AA1" s="7"/>
-      <c r="AB1" s="7"/>
-      <c r="AC1" s="7" t="s">
+      <c r="Y1" s="14"/>
+      <c r="Z1" s="14"/>
+      <c r="AA1" s="14"/>
+      <c r="AB1" s="14"/>
+      <c r="AC1" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="AD1" s="7"/>
-      <c r="AE1" s="7"/>
-      <c r="AF1" s="7"/>
-      <c r="AG1" s="7"/>
+      <c r="AD1" s="14"/>
+      <c r="AE1" s="14"/>
+      <c r="AF1" s="14"/>
+      <c r="AG1" s="14"/>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -936,26 +936,26 @@
       <c r="P2" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="Q2" s="9"/>
-      <c r="R2" s="9"/>
+      <c r="Q2" s="16"/>
+      <c r="R2" s="16"/>
       <c r="S2" s="4"/>
       <c r="T2" s="4"/>
       <c r="U2" s="4"/>
       <c r="V2" s="4"/>
       <c r="W2" s="4"/>
-      <c r="X2" s="9"/>
-      <c r="Y2" s="9"/>
-      <c r="Z2" s="9"/>
-      <c r="AA2" s="9"/>
-      <c r="AB2" s="9"/>
-      <c r="AC2" s="10"/>
-      <c r="AD2" s="12"/>
-      <c r="AE2" s="12"/>
-      <c r="AF2" s="12"/>
-      <c r="AG2" s="12"/>
-      <c r="AI2" s="6"/>
-      <c r="AJ2" s="6"/>
-      <c r="AK2" s="6"/>
+      <c r="X2" s="16"/>
+      <c r="Y2" s="16"/>
+      <c r="Z2" s="16"/>
+      <c r="AA2" s="16"/>
+      <c r="AB2" s="16"/>
+      <c r="AC2" s="15"/>
+      <c r="AD2" s="13"/>
+      <c r="AE2" s="13"/>
+      <c r="AF2" s="13"/>
+      <c r="AG2" s="13"/>
+      <c r="AI2" s="13"/>
+      <c r="AJ2" s="13"/>
+      <c r="AK2" s="13"/>
     </row>
     <row r="3" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
@@ -982,26 +982,26 @@
       <c r="H3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
       <c r="L3" s="2" t="s">
         <v>17</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="N3" s="8" t="s">
+      <c r="N3" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="O3" s="8"/>
-      <c r="P3" s="8"/>
-      <c r="Q3" s="8" t="s">
+      <c r="O3" s="9"/>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="R3" s="8"/>
+      <c r="R3" s="9"/>
       <c r="S3" s="2" t="s">
         <v>17</v>
       </c>
@@ -1017,20 +1017,20 @@
       <c r="W3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="X3" s="8" t="s">
+      <c r="X3" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="Y3" s="8"/>
-      <c r="Z3" s="8"/>
-      <c r="AA3" s="8"/>
-      <c r="AB3" s="8"/>
-      <c r="AC3" s="8" t="s">
+      <c r="Y3" s="9"/>
+      <c r="Z3" s="9"/>
+      <c r="AA3" s="9"/>
+      <c r="AB3" s="9"/>
+      <c r="AC3" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="AD3" s="8"/>
-      <c r="AE3" s="8"/>
-      <c r="AF3" s="8"/>
-      <c r="AG3" s="8"/>
+      <c r="AD3" s="9"/>
+      <c r="AE3" s="9"/>
+      <c r="AF3" s="9"/>
+      <c r="AG3" s="9"/>
     </row>
     <row r="4" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
@@ -1045,14 +1045,14 @@
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="4"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="16"/>
+      <c r="K4" s="16"/>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
-      <c r="N4" s="16"/>
-      <c r="O4" s="17"/>
-      <c r="P4" s="11"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="11"/>
+      <c r="P4" s="12"/>
       <c r="Q4" s="4"/>
       <c r="R4" s="4"/>
       <c r="S4" s="4"/>
@@ -1060,16 +1060,16 @@
       <c r="U4" s="4"/>
       <c r="V4" s="4"/>
       <c r="W4" s="4"/>
-      <c r="X4" s="9"/>
-      <c r="Y4" s="9"/>
-      <c r="Z4" s="9"/>
-      <c r="AA4" s="9"/>
-      <c r="AB4" s="9"/>
-      <c r="AC4" s="10"/>
-      <c r="AD4" s="6"/>
-      <c r="AE4" s="6"/>
-      <c r="AF4" s="6"/>
-      <c r="AG4" s="6"/>
+      <c r="X4" s="16"/>
+      <c r="Y4" s="16"/>
+      <c r="Z4" s="16"/>
+      <c r="AA4" s="16"/>
+      <c r="AB4" s="16"/>
+      <c r="AC4" s="15"/>
+      <c r="AD4" s="13"/>
+      <c r="AE4" s="13"/>
+      <c r="AF4" s="13"/>
+      <c r="AG4" s="13"/>
     </row>
     <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
@@ -1096,22 +1096,22 @@
       <c r="H5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="I5" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="14"/>
       <c r="L5" s="1" t="s">
         <v>53</v>
       </c>
       <c r="M5" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="N5" s="13" t="s">
+      <c r="N5" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="O5" s="14"/>
-      <c r="P5" s="15"/>
+      <c r="O5" s="7"/>
+      <c r="P5" s="8"/>
       <c r="Q5" s="1" t="s">
         <v>40</v>
       </c>
@@ -1133,20 +1133,21 @@
       <c r="W5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X5" s="7" t="s">
+      <c r="X5" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="Y5" s="7"/>
-      <c r="Z5" s="7"/>
-      <c r="AA5" s="7"/>
-      <c r="AB5" s="7"/>
-      <c r="AC5" s="7" t="s">
+      <c r="Y5" s="14"/>
+      <c r="Z5" s="14"/>
+      <c r="AA5" s="14"/>
+      <c r="AB5" s="14"/>
+      <c r="AC5" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="AD5" s="7"/>
-      <c r="AE5" s="7"/>
-      <c r="AF5" s="7"/>
-      <c r="AG5" s="7"/>
+      <c r="AD5" s="14"/>
+      <c r="AE5" s="14"/>
+      <c r="AF5" s="14"/>
+      <c r="AG5" s="14"/>
+      <c r="AH5" s="17"/>
     </row>
     <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
@@ -1427,6 +1428,12 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="AC5:AG5"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="Q2:R2"/>
     <mergeCell ref="N1:P1"/>
     <mergeCell ref="N3:P3"/>
     <mergeCell ref="N4:P4"/>
@@ -1437,18 +1444,12 @@
     <mergeCell ref="AC3:AG3"/>
     <mergeCell ref="Q1:R1"/>
     <mergeCell ref="Q3:R3"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="Q2:R2"/>
     <mergeCell ref="X1:AB1"/>
     <mergeCell ref="X2:AB2"/>
     <mergeCell ref="X3:AB3"/>
     <mergeCell ref="X4:AB4"/>
     <mergeCell ref="X5:AB5"/>
     <mergeCell ref="AC4:AG4"/>
-    <mergeCell ref="AC5:AG5"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/GameConfig/Datas/farmland/seed.xlsx
+++ b/Config/GameConfig/Datas/farmland/seed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UnityProject\Framework\Framework\Config\GameConfig\Datas\farmland\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5E9D45B-CB9C-4C03-A134-E757983FD961}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F178E43D-3B86-42C3-B83C-3D795CBB6B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="66">
   <si>
     <t>##var</t>
   </si>
@@ -329,6 +329,22 @@
   </si>
   <si>
     <t>触发稀有收获的额外产量</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>stageTime</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>阶段时间</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>只需要幼苗期</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>c</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -484,6 +500,16 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -491,9 +517,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
@@ -508,16 +531,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="差" xfId="2" builtinId="27"/>
@@ -800,37 +816,37 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AK9"/>
+  <dimension ref="A1:AL9"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="19.875" customWidth="1"/>
     <col min="5" max="6" width="13.625" customWidth="1"/>
     <col min="7" max="7" width="21.375" customWidth="1"/>
-    <col min="8" max="8" width="23.25" customWidth="1"/>
-    <col min="9" max="9" width="16.25" customWidth="1"/>
-    <col min="10" max="11" width="14.875" customWidth="1"/>
-    <col min="12" max="12" width="39.125" customWidth="1"/>
-    <col min="13" max="15" width="18" customWidth="1"/>
-    <col min="16" max="16" width="19.625" customWidth="1"/>
-    <col min="17" max="18" width="22.75" customWidth="1"/>
-    <col min="19" max="19" width="17.75" customWidth="1"/>
-    <col min="20" max="20" width="21" customWidth="1"/>
-    <col min="21" max="21" width="23.25" customWidth="1"/>
-    <col min="22" max="22" width="18.375" customWidth="1"/>
-    <col min="23" max="23" width="19.25" customWidth="1"/>
-    <col min="24" max="24" width="10.75" customWidth="1"/>
-    <col min="25" max="25" width="10.125" customWidth="1"/>
-    <col min="26" max="26" width="9.375" customWidth="1"/>
-    <col min="29" max="29" width="11.25" customWidth="1"/>
-    <col min="30" max="30" width="11.125" customWidth="1"/>
-    <col min="31" max="31" width="11.875" customWidth="1"/>
-    <col min="32" max="32" width="12.5" customWidth="1"/>
-    <col min="33" max="33" width="13.75" customWidth="1"/>
-    <col min="34" max="34" width="32" customWidth="1"/>
-    <col min="35" max="35" width="22.375" customWidth="1"/>
+    <col min="8" max="9" width="23.25" customWidth="1"/>
+    <col min="10" max="10" width="16.25" customWidth="1"/>
+    <col min="11" max="12" width="14.875" customWidth="1"/>
+    <col min="13" max="13" width="39.125" customWidth="1"/>
+    <col min="14" max="16" width="18" customWidth="1"/>
+    <col min="17" max="17" width="19.625" customWidth="1"/>
+    <col min="18" max="19" width="22.75" customWidth="1"/>
+    <col min="20" max="20" width="17.75" customWidth="1"/>
+    <col min="21" max="21" width="21" customWidth="1"/>
+    <col min="22" max="22" width="23.25" customWidth="1"/>
+    <col min="23" max="23" width="18.375" customWidth="1"/>
+    <col min="24" max="24" width="19.25" customWidth="1"/>
+    <col min="25" max="25" width="10.75" customWidth="1"/>
+    <col min="26" max="26" width="10.125" customWidth="1"/>
+    <col min="27" max="27" width="9.375" customWidth="1"/>
+    <col min="30" max="30" width="11.25" customWidth="1"/>
+    <col min="31" max="31" width="11.125" customWidth="1"/>
+    <col min="32" max="32" width="11.875" customWidth="1"/>
+    <col min="33" max="33" width="12.5" customWidth="1"/>
+    <col min="34" max="34" width="13.75" customWidth="1"/>
+    <col min="35" max="35" width="32" customWidth="1"/>
+    <col min="36" max="36" width="22.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -855,57 +871,60 @@
       <c r="H1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J1" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="1" t="s">
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="O1" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="O1" s="7"/>
-      <c r="P1" s="8"/>
-      <c r="Q1" s="14" t="s">
+      <c r="P1" s="11"/>
+      <c r="Q1" s="12"/>
+      <c r="R1" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="R1" s="14"/>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="7"/>
+      <c r="T1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="V1" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="X1" s="14" t="s">
+      <c r="Y1" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="Y1" s="14"/>
-      <c r="Z1" s="14"/>
-      <c r="AA1" s="14"/>
-      <c r="AB1" s="14"/>
-      <c r="AC1" s="14" t="s">
+      <c r="Z1" s="7"/>
+      <c r="AA1" s="7"/>
+      <c r="AB1" s="7"/>
+      <c r="AC1" s="7"/>
+      <c r="AD1" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="AD1" s="14"/>
-      <c r="AE1" s="14"/>
-      <c r="AF1" s="14"/>
-      <c r="AG1" s="14"/>
+      <c r="AE1" s="7"/>
+      <c r="AF1" s="7"/>
+      <c r="AG1" s="7"/>
+      <c r="AH1" s="7"/>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>36</v>
       </c>
@@ -916,48 +935,49 @@
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="4"/>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="4"/>
+      <c r="J2" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="K2" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="L2" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="L2" s="4"/>
       <c r="M2" s="4"/>
-      <c r="N2" s="4" t="s">
+      <c r="N2" s="4"/>
+      <c r="O2" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="P2" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="Q2" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="Q2" s="16"/>
-      <c r="R2" s="16"/>
-      <c r="S2" s="4"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="9"/>
       <c r="T2" s="4"/>
       <c r="U2" s="4"/>
       <c r="V2" s="4"/>
       <c r="W2" s="4"/>
-      <c r="X2" s="16"/>
-      <c r="Y2" s="16"/>
-      <c r="Z2" s="16"/>
-      <c r="AA2" s="16"/>
-      <c r="AB2" s="16"/>
-      <c r="AC2" s="15"/>
-      <c r="AD2" s="13"/>
-      <c r="AE2" s="13"/>
-      <c r="AF2" s="13"/>
-      <c r="AG2" s="13"/>
-      <c r="AI2" s="13"/>
-      <c r="AJ2" s="13"/>
-      <c r="AK2" s="13"/>
+      <c r="X2" s="4"/>
+      <c r="Y2" s="9"/>
+      <c r="Z2" s="9"/>
+      <c r="AA2" s="9"/>
+      <c r="AB2" s="9"/>
+      <c r="AC2" s="9"/>
+      <c r="AD2" s="17"/>
+      <c r="AE2" s="16"/>
+      <c r="AF2" s="16"/>
+      <c r="AG2" s="16"/>
+      <c r="AH2" s="16"/>
+      <c r="AJ2" s="16"/>
+      <c r="AK2" s="16"/>
+      <c r="AL2" s="16"/>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -982,57 +1002,60 @@
       <c r="H3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
       <c r="M3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="N3" s="9" t="s">
+      <c r="N3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="O3" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="O3" s="9"/>
-      <c r="P3" s="9"/>
-      <c r="Q3" s="9" t="s">
+      <c r="P3" s="8"/>
+      <c r="Q3" s="8"/>
+      <c r="R3" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="R3" s="9"/>
-      <c r="S3" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="S3" s="8"/>
       <c r="T3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="U3" s="5" t="s">
+      <c r="U3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V3" s="2" t="s">
+      <c r="V3" s="5" t="s">
         <v>17</v>
       </c>
       <c r="W3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="X3" s="9" t="s">
+      <c r="X3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y3" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="Y3" s="9"/>
-      <c r="Z3" s="9"/>
-      <c r="AA3" s="9"/>
-      <c r="AB3" s="9"/>
-      <c r="AC3" s="9" t="s">
+      <c r="Z3" s="8"/>
+      <c r="AA3" s="8"/>
+      <c r="AB3" s="8"/>
+      <c r="AC3" s="8"/>
+      <c r="AD3" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="AD3" s="9"/>
-      <c r="AE3" s="9"/>
-      <c r="AF3" s="9"/>
-      <c r="AG3" s="9"/>
+      <c r="AE3" s="8"/>
+      <c r="AF3" s="8"/>
+      <c r="AG3" s="8"/>
+      <c r="AH3" s="8"/>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
@@ -1045,33 +1068,36 @@
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="4"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="16"/>
-      <c r="K4" s="16"/>
-      <c r="L4" s="4"/>
+      <c r="I4" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
       <c r="M4" s="4"/>
-      <c r="N4" s="10"/>
-      <c r="O4" s="11"/>
-      <c r="P4" s="12"/>
-      <c r="Q4" s="4"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="13"/>
+      <c r="P4" s="14"/>
+      <c r="Q4" s="15"/>
       <c r="R4" s="4"/>
       <c r="S4" s="4"/>
       <c r="T4" s="4"/>
       <c r="U4" s="4"/>
       <c r="V4" s="4"/>
       <c r="W4" s="4"/>
-      <c r="X4" s="16"/>
-      <c r="Y4" s="16"/>
-      <c r="Z4" s="16"/>
-      <c r="AA4" s="16"/>
-      <c r="AB4" s="16"/>
-      <c r="AC4" s="15"/>
-      <c r="AD4" s="13"/>
-      <c r="AE4" s="13"/>
-      <c r="AF4" s="13"/>
-      <c r="AG4" s="13"/>
+      <c r="X4" s="4"/>
+      <c r="Y4" s="9"/>
+      <c r="Z4" s="9"/>
+      <c r="AA4" s="9"/>
+      <c r="AB4" s="9"/>
+      <c r="AC4" s="9"/>
+      <c r="AD4" s="17"/>
+      <c r="AE4" s="16"/>
+      <c r="AF4" s="16"/>
+      <c r="AG4" s="16"/>
+      <c r="AH4" s="16"/>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -1096,60 +1122,63 @@
       <c r="H5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I5" s="14" t="s">
+      <c r="I5" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="J5" s="14"/>
-      <c r="K5" s="14"/>
-      <c r="L5" s="1" t="s">
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="M5" s="1" t="s">
+      <c r="N5" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="N5" s="6" t="s">
+      <c r="O5" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="O5" s="7"/>
-      <c r="P5" s="8"/>
-      <c r="Q5" s="1" t="s">
+      <c r="P5" s="11"/>
+      <c r="Q5" s="12"/>
+      <c r="R5" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="R5" s="1" t="s">
+      <c r="S5" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="S5" s="1" t="s">
+      <c r="T5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="T5" s="1" t="s">
+      <c r="U5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U5" s="1" t="s">
+      <c r="V5" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="V5" s="1" t="s">
+      <c r="W5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W5" s="1" t="s">
+      <c r="X5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X5" s="14" t="s">
+      <c r="Y5" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="Y5" s="14"/>
-      <c r="Z5" s="14"/>
-      <c r="AA5" s="14"/>
-      <c r="AB5" s="14"/>
-      <c r="AC5" s="14" t="s">
+      <c r="Z5" s="7"/>
+      <c r="AA5" s="7"/>
+      <c r="AB5" s="7"/>
+      <c r="AC5" s="7"/>
+      <c r="AD5" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="AD5" s="14"/>
-      <c r="AE5" s="14"/>
-      <c r="AF5" s="14"/>
-      <c r="AG5" s="14"/>
-      <c r="AH5" s="17"/>
+      <c r="AE5" s="7"/>
+      <c r="AF5" s="7"/>
+      <c r="AG5" s="7"/>
+      <c r="AH5" s="7"/>
+      <c r="AI5" s="6"/>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>52</v>
       </c>
@@ -1160,16 +1189,18 @@
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
-      <c r="I6" s="3"/>
+      <c r="I6" s="1" t="s">
+        <v>64</v>
+      </c>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
-      <c r="L6" s="1" t="s">
+      <c r="L6" s="3"/>
+      <c r="M6" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="M6" s="1" t="s">
+      <c r="N6" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="N6" s="1"/>
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
@@ -1179,38 +1210,39 @@
       <c r="U6" s="1"/>
       <c r="V6" s="1"/>
       <c r="W6" s="1"/>
-      <c r="X6" s="3">
+      <c r="X6" s="1"/>
+      <c r="Y6" s="3">
         <v>2</v>
       </c>
-      <c r="Y6" s="3">
+      <c r="Z6" s="3">
         <v>3</v>
       </c>
-      <c r="Z6" s="3">
+      <c r="AA6" s="3">
         <v>4</v>
       </c>
-      <c r="AA6" s="3">
+      <c r="AB6" s="3">
         <v>5</v>
       </c>
-      <c r="AB6" s="3">
+      <c r="AC6" s="3">
         <v>6</v>
       </c>
-      <c r="AC6" s="3">
+      <c r="AD6" s="3">
         <v>2</v>
       </c>
-      <c r="AD6" s="3">
+      <c r="AE6" s="3">
         <v>3</v>
       </c>
-      <c r="AE6" s="3">
+      <c r="AF6" s="3">
         <v>4</v>
       </c>
-      <c r="AF6" s="3">
+      <c r="AG6" s="3">
         <v>5</v>
       </c>
-      <c r="AG6" s="3">
+      <c r="AH6" s="3">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B7">
         <v>1100001</v>
       </c>
@@ -1233,52 +1265,55 @@
         <v>5</v>
       </c>
       <c r="I7">
+        <v>2</v>
+      </c>
+      <c r="J7">
         <v>1110001</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>5</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>10</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>50</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <v>1</v>
       </c>
-      <c r="N7">
+      <c r="O7">
         <v>1110001</v>
       </c>
-      <c r="O7">
+      <c r="P7">
         <v>20</v>
       </c>
-      <c r="P7">
+      <c r="Q7">
         <v>30</v>
       </c>
-      <c r="Q7">
+      <c r="R7">
         <v>2</v>
       </c>
-      <c r="R7">
+      <c r="S7">
         <v>3</v>
       </c>
-      <c r="S7">
+      <c r="T7">
         <v>2</v>
       </c>
-      <c r="T7">
+      <c r="U7">
         <v>1</v>
-      </c>
-      <c r="U7">
-        <v>0</v>
       </c>
       <c r="V7">
         <v>0</v>
       </c>
       <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B8">
         <v>1100002</v>
       </c>
@@ -1301,52 +1336,55 @@
         <v>10</v>
       </c>
       <c r="I8">
+        <v>3</v>
+      </c>
+      <c r="J8">
         <v>1110002</v>
       </c>
-      <c r="J8">
+      <c r="K8">
         <v>6</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>12</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>50</v>
       </c>
-      <c r="M8">
+      <c r="N8">
         <v>3</v>
       </c>
-      <c r="N8">
+      <c r="O8">
         <v>1110002</v>
       </c>
-      <c r="O8">
+      <c r="P8">
         <v>25</v>
       </c>
-      <c r="P8">
+      <c r="Q8">
         <v>40</v>
       </c>
-      <c r="Q8">
+      <c r="R8">
         <v>2</v>
       </c>
-      <c r="R8">
+      <c r="S8">
         <v>4</v>
-      </c>
-      <c r="S8">
-        <v>2</v>
       </c>
       <c r="T8">
         <v>2</v>
       </c>
       <c r="U8">
+        <v>2</v>
+      </c>
+      <c r="V8">
         <v>15</v>
       </c>
-      <c r="V8">
+      <c r="W8">
         <v>2</v>
       </c>
-      <c r="W8">
+      <c r="X8">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B9">
         <v>1100003</v>
       </c>
@@ -1369,87 +1407,90 @@
         <v>20</v>
       </c>
       <c r="I9">
+        <v>8</v>
+      </c>
+      <c r="J9">
         <v>1110003</v>
       </c>
-      <c r="J9">
+      <c r="K9">
         <v>7</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>15</v>
       </c>
-      <c r="L9">
+      <c r="M9">
         <v>50</v>
       </c>
-      <c r="M9">
+      <c r="N9">
         <v>5</v>
       </c>
-      <c r="N9">
+      <c r="O9">
         <v>1110003</v>
       </c>
-      <c r="O9">
+      <c r="P9">
         <v>30</v>
       </c>
-      <c r="P9">
+      <c r="Q9">
         <v>50</v>
       </c>
-      <c r="Q9">
+      <c r="R9">
         <v>3</v>
       </c>
-      <c r="R9">
+      <c r="S9">
         <v>5</v>
       </c>
-      <c r="S9">
+      <c r="T9">
         <v>3</v>
       </c>
-      <c r="T9">
+      <c r="U9">
         <v>2</v>
       </c>
-      <c r="U9">
+      <c r="V9">
         <v>25</v>
       </c>
-      <c r="V9">
+      <c r="W9">
         <v>1</v>
       </c>
-      <c r="W9">
+      <c r="X9">
         <v>3</v>
       </c>
-      <c r="X9">
+      <c r="Y9">
         <v>10</v>
       </c>
-      <c r="Y9">
+      <c r="Z9">
         <v>5</v>
       </c>
-      <c r="AC9">
+      <c r="AD9">
         <v>-30</v>
       </c>
-      <c r="AD9">
+      <c r="AE9">
         <v>-50</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="AC5:AG5"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="Q2:R2"/>
-    <mergeCell ref="N1:P1"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="N5:P5"/>
-    <mergeCell ref="AI2:AK2"/>
-    <mergeCell ref="AC1:AG1"/>
-    <mergeCell ref="AC2:AG2"/>
-    <mergeCell ref="AC3:AG3"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="Q3:R3"/>
-    <mergeCell ref="X1:AB1"/>
-    <mergeCell ref="X2:AB2"/>
-    <mergeCell ref="X3:AB3"/>
-    <mergeCell ref="X4:AB4"/>
-    <mergeCell ref="X5:AB5"/>
-    <mergeCell ref="AC4:AG4"/>
+    <mergeCell ref="AJ2:AL2"/>
+    <mergeCell ref="AD1:AH1"/>
+    <mergeCell ref="AD2:AH2"/>
+    <mergeCell ref="AD3:AH3"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="Y1:AC1"/>
+    <mergeCell ref="Y2:AC2"/>
+    <mergeCell ref="Y3:AC3"/>
+    <mergeCell ref="AD5:AH5"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="J3:L3"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="J1:L1"/>
+    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="O1:Q1"/>
+    <mergeCell ref="O3:Q3"/>
+    <mergeCell ref="O4:Q4"/>
+    <mergeCell ref="O5:Q5"/>
+    <mergeCell ref="Y4:AC4"/>
+    <mergeCell ref="Y5:AC5"/>
+    <mergeCell ref="AD4:AH4"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
